--- a/examples/01_TiO2_on_BK7_65deg.xlsx
+++ b/examples/01_TiO2_on_BK7_65deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4049,10 +4049,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Возможные дефекты</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/01_TiO2_on_BK7_65deg.xlsx
+++ b/examples/01_TiO2_on_BK7_65deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3971,100 +3971,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>65</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±5</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>400 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/01_TiO2_on_BK7_65deg.xlsx
+++ b/examples/01_TiO2_on_BK7_65deg.xlsx
@@ -478,16 +478,16 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>12.4559</v>
+        <v>12.423</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>327.22</v>
+        <v>325.5703</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1822</v>
+        <v>0.1826</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13.5421</v>
+        <v>13.5603</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34.8617</v>
+        <v>36.1283</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1674</v>
+        <v>0.1672</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +512,16 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13.933</v>
+        <v>13.9413</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>83.2683</v>
+        <v>84.30289999999999</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1614</v>
+        <v>0.1613</v>
       </c>
     </row>
     <row r="5">
@@ -529,16 +529,16 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>14.5713</v>
+        <v>14.5816</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>112.8034</v>
+        <v>113.2049</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1536</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="6">
@@ -546,16 +546,16 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>15.2788</v>
+        <v>15.2856</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>134.4123</v>
+        <v>134.5763</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1459</v>
+        <v>0.1458</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>15.6767</v>
+        <v>15.6808</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>153.5736</v>
+        <v>153.6388</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1411</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="8">
@@ -580,10 +580,10 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15.7122</v>
+        <v>15.7156</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>171.4613</v>
+        <v>171.4707</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
@@ -597,16 +597,16 @@
         <v>414</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>15.1965</v>
+        <v>15.2009</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>189.461</v>
+        <v>189.4228</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1425</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="10">
@@ -614,10 +614,10 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>14.3452</v>
+        <v>14.352</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>208.0202</v>
+        <v>207.9194</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
@@ -631,16 +631,16 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.2732</v>
+        <v>13.2827</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>228.4459</v>
+        <v>228.2298</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.1582</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12.3438</v>
+        <v>12.3515</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>253.0007</v>
+        <v>252.5326</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1684</v>
+        <v>0.1683</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>422</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>11.9245</v>
+        <v>11.9133</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>285.9398</v>
+        <v>285.0028</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.172</v>
+        <v>0.1722</v>
       </c>
     </row>
     <row r="14">
@@ -682,16 +682,16 @@
         <v>424</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12.5866</v>
+        <v>12.5676</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>331.2333</v>
+        <v>330.3257</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.162</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="15">
@@ -699,16 +699,16 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>13.4197</v>
+        <v>13.4306</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>23.1938</v>
+        <v>23.7409</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1511</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="16">
@@ -716,10 +716,10 @@
         <v>428</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>13.5292</v>
+        <v>13.528</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>65.4674</v>
+        <v>66.29389999999999</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
@@ -733,10 +733,10 @@
         <v>430</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>13.6471</v>
+        <v>13.6491</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>94.28619999999999</v>
+        <v>94.7281</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
@@ -750,10 +750,10 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>14.0058</v>
+        <v>14.0097</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>115.5446</v>
+        <v>115.7585</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
@@ -767,10 +767,10 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>14.3689</v>
+        <v>14.372</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>133.0763</v>
+        <v>133.1841</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
@@ -784,16 +784,16 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>14.6312</v>
+        <v>14.6334</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>148.9025</v>
+        <v>148.9564</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.1332</v>
+        <v>0.1331</v>
       </c>
     </row>
     <row r="21">
@@ -801,10 +801,10 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>14.6659</v>
+        <v>14.6676</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>163.6333</v>
+        <v>163.6544</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
@@ -818,10 +818,10 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>14.4792</v>
+        <v>14.4811</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>178.366</v>
+        <v>178.3619</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
@@ -835,10 +835,10 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>14.1265</v>
+        <v>14.1289</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>192.994</v>
+        <v>192.9645</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
@@ -852,16 +852,16 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13.4924</v>
+        <v>13.4958</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>208.4567</v>
+        <v>208.3942</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.1383</v>
+        <v>0.1382</v>
       </c>
     </row>
     <row r="25">
@@ -869,16 +869,16 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>12.8686</v>
+        <v>12.8728</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>224.8172</v>
+        <v>224.7026</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1439</v>
+        <v>0.1438</v>
       </c>
     </row>
     <row r="26">
@@ -886,10 +886,10 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>12.1483</v>
+        <v>12.1522</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>243.1955</v>
+        <v>242.9893</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
@@ -903,10 +903,10 @@
         <v>450</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>11.7112</v>
+        <v>11.7104</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>264.674</v>
+        <v>264.3065</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
@@ -920,16 +920,16 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>11.7806</v>
+        <v>11.7685</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>292.1034</v>
+        <v>291.5184</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.1511</v>
+        <v>0.1513</v>
       </c>
     </row>
     <row r="29">
@@ -937,16 +937,16 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>12.5456</v>
+        <v>12.532</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>326.7354</v>
+        <v>326.1576</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.1418</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="30">
@@ -954,16 +954,16 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>13.3035</v>
+        <v>13.3094</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5.6799</v>
+        <v>5.7158</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.1328</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="31">
@@ -971,10 +971,10 @@
         <v>458</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>13.4767</v>
+        <v>13.4772</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42.4256</v>
+        <v>42.9415</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
@@ -988,10 +988,10 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>13.2559</v>
+        <v>13.2518</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>70.8154</v>
+        <v>71.26009999999999</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
@@ -1005,10 +1005,10 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13.191</v>
+        <v>13.1899</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>92.8544</v>
+        <v>93.1246</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
@@ -1022,10 +1022,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13.2928</v>
+        <v>13.2937</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>109.9997</v>
+        <v>110.1553</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
@@ -1039,10 +1039,10 @@
         <v>466</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13.4718</v>
+        <v>13.4731</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>124.6636</v>
+        <v>124.7549</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
@@ -1056,10 +1056,10 @@
         <v>468</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>13.6863</v>
+        <v>13.6875</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>138.0473</v>
+        <v>138.1015</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
@@ -1073,10 +1073,10 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>13.8197</v>
+        <v>13.8206</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>150.6725</v>
+        <v>150.7034</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
@@ -1090,10 +1090,10 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13.738</v>
+        <v>13.7388</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>162.6093</v>
+        <v>162.624</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
@@ -1107,10 +1107,10 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>13.6439</v>
+        <v>13.6448</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>174.4541</v>
+        <v>174.4558</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
@@ -1124,10 +1124,10 @@
         <v>476</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13.4045</v>
+        <v>13.4056</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>186.6142</v>
+        <v>186.6034</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
@@ -1141,16 +1141,16 @@
         <v>478</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>13.0933</v>
+        <v>13.0946</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>198.7122</v>
+        <v>198.6876</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.1222</v>
+        <v>0.1221</v>
       </c>
     </row>
     <row r="42">
@@ -1158,16 +1158,16 @@
         <v>480</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>12.6379</v>
+        <v>12.6395</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>211.2044</v>
+        <v>211.1619</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.1248</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="43">
@@ -1175,10 +1175,10 @@
         <v>482</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>12.1862</v>
+        <v>12.188</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>224.4749</v>
+        <v>224.407</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
@@ -1192,10 +1192,10 @@
         <v>484</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>11.8475</v>
+        <v>11.849</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>238.8048</v>
+        <v>238.6986</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
@@ -1212,7 +1212,7 @@
         <v>11.5151</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>254.9532</v>
+        <v>254.7884</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
@@ -1226,10 +1226,10 @@
         <v>488</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>11.4197</v>
+        <v>11.416</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>272.8214</v>
+        <v>272.5727</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
@@ -1243,16 +1243,16 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>11.7361</v>
+        <v>11.7272</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>294.3348</v>
+        <v>293.9941</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.128</v>
+        <v>0.1281</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>492</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>12.3646</v>
+        <v>12.3548</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>319.7815</v>
+        <v>319.4249</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.1208</v>
+        <v>0.1209</v>
       </c>
     </row>
     <row r="49">
@@ -1277,10 +1277,10 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13.0799</v>
+        <v>13.0797</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>348.6851</v>
+        <v>348.5214</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
@@ -1294,10 +1294,10 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13.4405</v>
+        <v>13.4448</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>18.0401</v>
+        <v>18.1926</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
@@ -1311,10 +1311,10 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>13.4116</v>
+        <v>13.4099</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>44.1794</v>
+        <v>44.4829</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
@@ -1328,16 +1328,16 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>13.0178</v>
+        <v>13.0135</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>65.9217</v>
+        <v>66.1942</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.111</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="53">
@@ -1345,10 +1345,10 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>12.807</v>
+        <v>12.8042</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>83.7222</v>
+        <v>83.9161</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
@@ -1362,10 +1362,10 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>12.7074</v>
+        <v>12.7063</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>98.65049999999999</v>
+        <v>98.77979999999999</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
@@ -1379,10 +1379,10 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>12.7469</v>
+        <v>12.7468</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>111.3602</v>
+        <v>111.446</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
@@ -1396,10 +1396,10 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>12.7776</v>
+        <v>12.7779</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>122.9381</v>
+        <v>122.9956</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
@@ -1413,10 +1413,10 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>12.8501</v>
+        <v>12.8505</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>133.7335</v>
+        <v>133.7722</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
@@ -1430,10 +1430,10 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>12.9396</v>
+        <v>12.94</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>144.2321</v>
+        <v>144.2578</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
@@ -1447,10 +1447,10 @@
         <v>514</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>12.9686</v>
+        <v>12.969</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>154.106</v>
+        <v>154.1221</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
@@ -1464,10 +1464,10 @@
         <v>516</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>12.8643</v>
+        <v>12.8647</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>163.8693</v>
+        <v>163.8779</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
@@ -1481,10 +1481,10 @@
         <v>518</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>12.8123</v>
+        <v>12.8127</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>173.3893</v>
+        <v>173.3914</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
@@ -1498,16 +1498,16 @@
         <v>520</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>12.6572</v>
+        <v>12.6577</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>182.6497</v>
+        <v>182.6457</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="63">
@@ -1515,10 +1515,10 @@
         <v>522</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>12.4311</v>
+        <v>12.4317</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>192.658</v>
+        <v>192.6477</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
@@ -1532,10 +1532,10 @@
         <v>524</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>12.1606</v>
+        <v>12.1613</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>202.2891</v>
+        <v>202.2718</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
@@ -1549,10 +1549,10 @@
         <v>526</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>11.9605</v>
+        <v>11.9612</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>212.2878</v>
+        <v>212.2617</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
@@ -1566,10 +1566,10 @@
         <v>528</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>11.6626</v>
+        <v>11.6633</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>222.7804</v>
+        <v>222.7431</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
@@ -1583,10 +1583,10 @@
         <v>530</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>11.4144</v>
+        <v>11.4149</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>234.0285</v>
+        <v>233.976</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
@@ -1603,7 +1603,7 @@
         <v>11.2559</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>245.5938</v>
+        <v>245.5209</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
@@ -1617,10 +1617,10 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>11.138</v>
+        <v>11.137</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>258.2786</v>
+        <v>258.1782</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
@@ -1634,10 +1634,10 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>11.2121</v>
+        <v>11.2094</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>272.2691</v>
+        <v>272.1338</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
@@ -1651,10 +1651,10 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>11.5128</v>
+        <v>11.5079</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>287.7315</v>
+        <v>287.5574</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
@@ -1668,10 +1668,10 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>11.933</v>
+        <v>11.9264</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>305.0419</v>
+        <v>304.8394</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
@@ -1685,10 +1685,10 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>12.5707</v>
+        <v>12.5655</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>324.67</v>
+        <v>324.4803</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
@@ -1702,10 +1702,10 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13.1414</v>
+        <v>13.141</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>345.6339</v>
+        <v>345.5281</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
@@ -1719,10 +1719,10 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13.4638</v>
+        <v>13.4667</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>7.4589</v>
+        <v>7.4872</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
@@ -1736,10 +1736,10 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13.4731</v>
+        <v>13.474</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>28.2096</v>
+        <v>28.3453</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
@@ -1753,10 +1753,10 @@
         <v>550</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>13.2161</v>
+        <v>13.2139</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46.8954</v>
+        <v>47.0669</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
@@ -1770,10 +1770,10 @@
         <v>552</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>12.8899</v>
+        <v>12.8866</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>63.0126</v>
+        <v>63.1689</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
@@ -1787,10 +1787,10 @@
         <v>554</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>12.5916</v>
+        <v>12.5889</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>76.7988</v>
+        <v>76.92310000000001</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
@@ -1804,16 +1804,16 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>12.3895</v>
+        <v>12.3877</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>89.10680000000001</v>
+        <v>89.2004</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.0935</v>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="81">
@@ -1821,10 +1821,10 @@
         <v>558</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>12.27</v>
+        <v>12.269</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>99.7319</v>
+        <v>99.80110000000001</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
@@ -1838,10 +1838,10 @@
         <v>560</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>12.2401</v>
+        <v>12.2396</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>109.755</v>
+        <v>109.8062</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
@@ -1855,10 +1855,10 @@
         <v>562</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>12.1844</v>
+        <v>12.1842</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>118.8018</v>
+        <v>118.8398</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
@@ -1875,7 +1875,7 @@
         <v>12.1744</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>127.3942</v>
+        <v>127.4224</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
@@ -1889,10 +1889,10 @@
         <v>566</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>12.177</v>
+        <v>12.1771</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>135.887</v>
+        <v>135.9079</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
@@ -1906,10 +1906,10 @@
         <v>568</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>12.213</v>
+        <v>12.2132</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>143.6669</v>
+        <v>143.6822</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
@@ -1923,10 +1923,10 @@
         <v>570</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>12.2031</v>
+        <v>12.2033</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>151.6038</v>
+        <v>151.6147</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
@@ -1940,10 +1940,10 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>12.1874</v>
+        <v>12.1876</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>159.0946</v>
+        <v>159.1018</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
@@ -1957,10 +1957,10 @@
         <v>574</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>12.1132</v>
+        <v>12.1133</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>166.7048</v>
+        <v>166.7087</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
@@ -1974,10 +1974,10 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>12.0081</v>
+        <v>12.0083</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>174.2928</v>
+        <v>174.2939</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
@@ -1991,10 +1991,10 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>11.9059</v>
+        <v>11.9061</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>181.8625</v>
+        <v>181.8609</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
@@ -2008,10 +2008,10 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>11.7728</v>
+        <v>11.773</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>189.4871</v>
+        <v>189.4826</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
@@ -2025,10 +2025,10 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>11.6333</v>
+        <v>11.6336</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>197.1354</v>
+        <v>197.1279</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
@@ -2042,10 +2042,10 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>11.4953</v>
+        <v>11.4955</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>204.8643</v>
+        <v>204.8535</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
@@ -2059,10 +2059,10 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>11.3271</v>
+        <v>11.3273</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>212.6745</v>
+        <v>212.6598</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
@@ -2076,10 +2076,10 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>11.1843</v>
+        <v>11.1845</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>220.6464</v>
+        <v>220.627</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
@@ -2093,10 +2093,10 @@
         <v>590</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>11.086</v>
+        <v>11.0861</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>229.0587</v>
+        <v>229.0336</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
@@ -2113,7 +2113,7 @@
         <v>10.9679</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>237.6076</v>
+        <v>237.5757</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
@@ -2127,10 +2127,10 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>10.8927</v>
+        <v>10.8925</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>246.8923</v>
+        <v>246.8518</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>10.8777</v>
+        <v>10.877</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>256.27</v>
+        <v>256.2191</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2161,10 +2161,10 @@
         <v>598</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>10.9634</v>
+        <v>10.9621</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>266.1568</v>
+        <v>266.0934</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2178,16 +2178,16 @@
         <v>600</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>11.1305</v>
+        <v>11.1284</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>276.6897</v>
+        <v>276.612</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0919</v>
       </c>
     </row>
     <row r="103">
@@ -2195,10 +2195,10 @@
         <v>602</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>11.3665</v>
+        <v>11.3634</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>288.1202</v>
+        <v>288.0278</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2212,16 +2212,16 @@
         <v>604</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>11.7401</v>
+        <v>11.7363</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>300.7691</v>
+        <v>300.6646</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0157</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.0864</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -2229,10 +2229,10 @@
         <v>606</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>12.2047</v>
+        <v>12.201</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>313.8315</v>
+        <v>313.7233</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
@@ -2246,16 +2246,16 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>12.7245</v>
+        <v>12.722</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>328.2655</v>
+        <v>328.1697</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="107">
@@ -2263,10 +2263,10 @@
         <v>610</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>13.1406</v>
+        <v>13.1403</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>343.4817</v>
+        <v>343.4197</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
@@ -2280,10 +2280,10 @@
         <v>612</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>13.4289</v>
+        <v>13.4303</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>359.0731</v>
+        <v>359.0617</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
@@ -2297,10 +2297,10 @@
         <v>614</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13.5353</v>
+        <v>13.5368</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>14.8103</v>
+        <v>14.8504</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
@@ -2314,10 +2314,10 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13.4331</v>
+        <v>13.4333</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>29.523</v>
+        <v>29.5989</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
@@ -2331,10 +2331,10 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>13.1669</v>
+        <v>13.1656</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>42.9955</v>
+        <v>43.086</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
@@ -2348,10 +2348,10 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>12.8934</v>
+        <v>12.8913</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>55.1317</v>
+        <v>55.2205</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
@@ -2365,16 +2365,16 @@
         <v>622</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>12.5797</v>
+        <v>12.5775</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>66.3026</v>
+        <v>66.3813</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.0788</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="114">
@@ -2382,10 +2382,10 @@
         <v>624</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>12.3268</v>
+        <v>12.3249</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>76.19670000000001</v>
+        <v>76.2628</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
@@ -2399,10 +2399,10 @@
         <v>626</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>12.1272</v>
+        <v>12.1257</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>85.2936</v>
+        <v>85.3477</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
@@ -2416,10 +2416,10 @@
         <v>628</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>11.9233</v>
+        <v>11.9223</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>93.4686</v>
+        <v>93.51220000000001</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
@@ -2433,10 +2433,10 @@
         <v>630</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>11.814</v>
+        <v>11.8133</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>101.4837</v>
+        <v>101.5189</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
@@ -2450,10 +2450,10 @@
         <v>632</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>11.7597</v>
+        <v>11.7592</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>108.6786</v>
+        <v>108.7069</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
@@ -2467,10 +2467,10 @@
         <v>634</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>11.7011</v>
+        <v>11.7008</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>115.5437</v>
+        <v>115.5665</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
@@ -2484,10 +2484,10 @@
         <v>636</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>11.6564</v>
+        <v>11.6562</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>122.1581</v>
+        <v>122.1765</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
@@ -2501,10 +2501,10 @@
         <v>638</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>11.6335</v>
+        <v>11.6334</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>128.5528</v>
+        <v>128.5676</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
@@ -2518,10 +2518,10 @@
         <v>640</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>11.5909</v>
+        <v>11.5908</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>134.8759</v>
+        <v>134.8878</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
@@ -2538,7 +2538,7 @@
         <v>11.5927</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>141.0448</v>
+        <v>141.0543</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2555,7 +2555,7 @@
         <v>11.5354</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>147.0256</v>
+        <v>147.033</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
@@ -2569,10 +2569,10 @@
         <v>646</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>11.5389</v>
+        <v>11.539</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>153.0244</v>
+        <v>153.0301</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
@@ -2589,7 +2589,7 @@
         <v>11.4899</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>158.8541</v>
+        <v>158.8583</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
@@ -2606,7 +2606,7 @@
         <v>11.4744</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>164.822</v>
+        <v>164.8248</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
@@ -2623,7 +2623,7 @@
         <v>11.4088</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>170.2643</v>
+        <v>170.2659</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
@@ -2637,10 +2637,10 @@
         <v>654</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>11.3449</v>
+        <v>11.345</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>176.0524</v>
+        <v>176.0528</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
@@ -2654,10 +2654,10 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>11.2741</v>
+        <v>11.2742</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>181.8887</v>
+        <v>181.8879</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
@@ -2671,10 +2671,10 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>11.2135</v>
+        <v>11.2136</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>187.6187</v>
+        <v>187.6168</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
@@ -2688,10 +2688,10 @@
         <v>660</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>11.1026</v>
+        <v>11.1027</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>193.3715</v>
+        <v>193.3683</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
@@ -2705,10 +2705,10 @@
         <v>662</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>11.0516</v>
+        <v>11.0517</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>199.0936</v>
+        <v>199.0892</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
@@ -2722,10 +2722,10 @@
         <v>664</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>10.942</v>
+        <v>10.9421</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>204.9999</v>
+        <v>204.9941</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
@@ -2742,7 +2742,7 @@
         <v>10.8569</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>211.0419</v>
+        <v>211.0347</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
@@ -2756,10 +2756,10 @@
         <v>668</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>10.8016</v>
+        <v>10.8017</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>217.1981</v>
+        <v>217.1891</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
@@ -2776,7 +2776,7 @@
         <v>10.72</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>222.9747</v>
+        <v>222.9639</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
@@ -2790,10 +2790,10 @@
         <v>672</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>10.6513</v>
+        <v>10.6512</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>229.1678</v>
+        <v>229.1548</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
@@ -2807,10 +2807,10 @@
         <v>674</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>10.6046</v>
+        <v>10.6045</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>235.5856</v>
+        <v>235.5702</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
@@ -2824,10 +2824,10 @@
         <v>676</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>10.6028</v>
+        <v>10.6026</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>241.8988</v>
+        <v>241.8804</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
@@ -2841,10 +2841,10 @@
         <v>678</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>10.5917</v>
+        <v>10.5914</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>248.7415</v>
+        <v>248.7199</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
@@ -2858,10 +2858,10 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>10.5953</v>
+        <v>10.5949</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>255.3378</v>
+        <v>255.3125</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
@@ -2875,16 +2875,16 @@
         <v>682</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>10.7256</v>
+        <v>10.725</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>262.6237</v>
+        <v>262.5942</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -2892,10 +2892,10 @@
         <v>684</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>10.8244</v>
+        <v>10.8235</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>269.9267</v>
+        <v>269.8926</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
@@ -2909,10 +2909,10 @@
         <v>686</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>10.9934</v>
+        <v>10.9921</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>277.4878</v>
+        <v>277.4486</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
@@ -2926,10 +2926,10 @@
         <v>688</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>11.1962</v>
+        <v>11.1946</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>285.4706</v>
+        <v>285.4263</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
@@ -2943,10 +2943,10 @@
         <v>690</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>11.4792</v>
+        <v>11.4773</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>293.9643</v>
+        <v>293.9153</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
@@ -2960,10 +2960,10 @@
         <v>692</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>11.8172</v>
+        <v>11.8152</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>302.9717</v>
+        <v>302.9191</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
@@ -2977,10 +2977,10 @@
         <v>694</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>12.1881</v>
+        <v>12.1861</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>312.0664</v>
+        <v>312.0124</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,10 +2994,10 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>12.5551</v>
+        <v>12.5535</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>321.9071</v>
+        <v>321.8556</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
@@ -3011,10 +3011,10 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>12.9041</v>
+        <v>12.9031</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>332.2178</v>
+        <v>332.1736</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
@@ -3028,10 +3028,10 @@
         <v>700</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13.2193</v>
+        <v>13.2192</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>343.0091</v>
+        <v>342.9777</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
@@ -3045,10 +3045,10 @@
         <v>702</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13.4548</v>
+        <v>13.4554</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>353.8087</v>
+        <v>353.7945</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3062,16 +3062,16 @@
         <v>704</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13.5865</v>
+        <v>13.5874</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>4.7647</v>
+        <v>4.7694</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.0723</v>
+        <v>0.0722</v>
       </c>
     </row>
     <row r="155">
@@ -3079,10 +3079,10 @@
         <v>706</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>13.6052</v>
+        <v>13.606</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>15.4685</v>
+        <v>15.4905</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
@@ -3096,10 +3096,10 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13.4825</v>
+        <v>13.4827</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>25.7437</v>
+        <v>25.7786</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
@@ -3113,10 +3113,10 @@
         <v>710</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13.2944</v>
+        <v>13.2939</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>35.5398</v>
+        <v>35.5823</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
@@ -3130,10 +3130,10 @@
         <v>712</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13.0785</v>
+        <v>13.0775</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>44.7197</v>
+        <v>44.765</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3147,10 +3147,10 @@
         <v>714</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>12.8163</v>
+        <v>12.815</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>53.1762</v>
+        <v>53.2205</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
@@ -3164,10 +3164,10 @@
         <v>716</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>12.5609</v>
+        <v>12.5596</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>61.1636</v>
+        <v>61.2048</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
@@ -3181,10 +3181,10 @@
         <v>718</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>12.3097</v>
+        <v>12.3084</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>68.5429</v>
+        <v>68.58</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
@@ -3198,10 +3198,10 @@
         <v>720</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>12.1114</v>
+        <v>12.1103</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>75.4631</v>
+        <v>75.4958</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3215,10 +3215,10 @@
         <v>722</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>11.9004</v>
+        <v>11.8995</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>81.874</v>
+        <v>81.90260000000001</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3232,10 +3232,10 @@
         <v>724</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>11.7405</v>
+        <v>11.7398</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>88.0438</v>
+        <v>88.0685</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3249,10 +3249,10 @@
         <v>726</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>11.609</v>
+        <v>11.6084</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>93.9739</v>
+        <v>93.9952</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3266,10 +3266,10 @@
         <v>728</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>11.4888</v>
+        <v>11.4884</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>99.4209</v>
+        <v>99.4392</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
@@ -3283,10 +3283,10 @@
         <v>730</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>11.3876</v>
+        <v>11.3873</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>104.7517</v>
+        <v>104.7674</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3300,10 +3300,10 @@
         <v>732</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>11.351</v>
+        <v>11.3508</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>109.9357</v>
+        <v>109.9491</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>11.2718</v>
+        <v>11.2716</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>114.9574</v>
+        <v>114.9689</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>11.2064</v>
+        <v>11.2063</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>119.6781</v>
+        <v>119.6881</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3351,10 +3351,10 @@
         <v>738</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>11.1794</v>
+        <v>11.1793</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>124.5504</v>
+        <v>124.559</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3368,10 +3368,10 @@
         <v>740</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>11.1152</v>
+        <v>11.1151</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>129.1319</v>
+        <v>129.1392</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3385,10 +3385,10 @@
         <v>742</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>11.0518</v>
+        <v>11.0517</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>133.8704</v>
+        <v>133.8768</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3405,7 +3405,7 @@
         <v>11.0856</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>138.1104</v>
+        <v>138.1158</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>11.0336</v>
+        <v>11.0335</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>142.6161</v>
+        <v>142.6206</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3439,7 +3439,7 @@
         <v>11.0199</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>147.0801</v>
+        <v>147.084</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3456,7 +3456,7 @@
         <v>10.9798</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>151.1753</v>
+        <v>151.1785</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3473,7 +3473,7 @@
         <v>10.927</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>155.6706</v>
+        <v>155.6733</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3490,7 +3490,7 @@
         <v>10.9253</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>159.8195</v>
+        <v>159.8216</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3507,7 +3507,7 @@
         <v>10.8882</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>164.1026</v>
+        <v>164.1042</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3524,7 +3524,7 @@
         <v>10.8516</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>168.3302</v>
+        <v>168.3313</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3541,7 +3541,7 @@
         <v>10.8148</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>172.4919</v>
+        <v>172.4926</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3558,7 +3558,7 @@
         <v>10.7958</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>176.5897</v>
+        <v>176.5899</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3575,7 +3575,7 @@
         <v>10.7436</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>180.634</v>
+        <v>180.6338</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3592,7 +3592,7 @@
         <v>10.6895</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>184.8902</v>
+        <v>184.8895</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3609,7 +3609,7 @@
         <v>10.6614</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>189.3104</v>
+        <v>189.3093</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3626,7 +3626,7 @@
         <v>10.6092</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>193.4281</v>
+        <v>193.4266</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3643,7 +3643,7 @@
         <v>10.5728</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>197.3685</v>
+        <v>197.3666</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3660,7 +3660,7 @@
         <v>10.5079</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>201.6794</v>
+        <v>201.677</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
@@ -3677,7 +3677,7 @@
         <v>10.4775</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>206.0427</v>
+        <v>206.0398</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3694,7 +3694,7 @@
         <v>10.4304</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>210.1969</v>
+        <v>210.1935</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3711,7 +3711,7 @@
         <v>10.4202</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>214.4869</v>
+        <v>214.483</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
@@ -3728,7 +3728,7 @@
         <v>10.3721</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>218.7295</v>
+        <v>218.725</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
@@ -3745,7 +3745,7 @@
         <v>10.3237</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>223.1676</v>
+        <v>223.1625</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
@@ -3762,7 +3762,7 @@
         <v>10.317</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>227.3599</v>
+        <v>227.354</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
@@ -3776,10 +3776,10 @@
         <v>788</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>10.3182</v>
+        <v>10.3181</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>232.0037</v>
+        <v>231.9971</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
@@ -3793,10 +3793,10 @@
         <v>790</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>10.2971</v>
+        <v>10.297</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>236.2981</v>
+        <v>236.2907</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
@@ -3810,10 +3810,10 @@
         <v>792</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>10.3348</v>
+        <v>10.3347</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>240.934</v>
+        <v>240.9257</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
@@ -3827,10 +3827,10 @@
         <v>794</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>10.3366</v>
+        <v>10.3364</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>245.404</v>
+        <v>245.3947</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
@@ -3844,10 +3844,10 @@
         <v>796</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>10.3562</v>
+        <v>10.356</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>250.1268</v>
+        <v>250.1165</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
@@ -3861,10 +3861,10 @@
         <v>798</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>10.4319</v>
+        <v>10.4316</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>254.7668</v>
+        <v>254.7554</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
@@ -3878,10 +3878,10 @@
         <v>800</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>10.489</v>
+        <v>10.4886</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>259.6304</v>
+        <v>259.6178</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
